--- a/data/faq_mapping.xlsx
+++ b/data/faq_mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20343"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seung\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\박준철\Desktop\임승원(20241101~)\20260915_chat-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B16B928-D65C-495F-80E2-591055AE32E1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB847213-B520-4BD8-B0FE-3FBE8B00858E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="20" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1160,10 +1160,6 @@
     <t>신청기간,신청자격,포기,변경,취소,비교,차이,채용,취업</t>
   </si>
   <si>
-    <t>📌 복수전공을 이수하면 원 전공과 복수전공 2개의 학위가 정식으로 발급되며, 두 학위 모두 졸업증명서 및 학위기에 기재됩니다.
-💡 대학원 지원 시 복수전공 학위가 입학 요건이나 전형에 어떻게 반영되는지는 대학원마다 다를 수 있으므로, 지원하고자 하는 대학원 사무실에 직접 확인하시길 권장합니다.</t>
-  </si>
-  <si>
     <t>F101</t>
   </si>
   <si>
@@ -1280,10 +1276,6 @@
   </si>
   <si>
     <t>부전공졸업증명서,부전공표기,부전공졸업증명,부전공졸업장,부전공기재,부전공어떻게표기,졸업증명서에,졸업증명서표기,어떻게표기,표기돼,표기되,증명서에표기</t>
-  </si>
-  <si>
-    <t>📌 부전공을 이수 완료한 경우 졸업증명서에 부전공 이수 사실이 표기됩니다.
-이수 중인 상태에서는 표기되지 않으며, 졸업 시점에 최종 확정됩니다.</t>
   </si>
   <si>
     <t>F114</t>
@@ -2925,215 +2917,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 2026-2학기 유연학사제도(다전공) 모집 신청기간: 2026. 8월까지
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>96137</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 2026-2학기 유연학사제도(다전공) 모집 신청기간: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>월까지</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>96137</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>F005</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3387,17 +3170,17 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>🔄</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학점교류 안내
+      <t>📝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 수강 관련 안내
 </t>
     </r>
     <r>
@@ -3417,7 +3200,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 학점교류란?
+      <t xml:space="preserve"> 수강신청:
 </t>
     </r>
     <r>
@@ -3437,27 +3220,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 종류:
+      <t xml:space="preserve"> 매 학기 개강 전 수강신청 기간에 수강신청 시스템(http://sugang.hknu.ac.kr)에서 신청
 </t>
     </r>
     <r>
@@ -3477,7 +3240,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 국내외 대학 학점교류 (협약 대학 간)
+      <t xml:space="preserve"> 수강신청 정정기간에 과목 변경 가능
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 수강철회:
 </t>
     </r>
     <r>
@@ -3497,27 +3280,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 계절학기 (여름/겨울 방학 중 타교 수강)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 유의사항:
+      <t xml:space="preserve"> 학기 중 수강철회 기간에 신청 가능
 </t>
     </r>
     <r>
@@ -3537,7 +3300,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 사전에 학점인정 신청 필요
+      <t xml:space="preserve"> 재수강과 다름 (재수강은 이전 성적 대체)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 성적 이의신청:
 </t>
     </r>
     <r>
@@ -3557,7 +3340,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 이수구분(전필, 전선, 교양 등) 확인 후 신청
+      <t xml:space="preserve"> 성적 공시 후 정정기간 내 신청
 </t>
     </r>
     <r>
@@ -3577,7 +3360,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 전공 및 학사지원팀 승인 필요
+      <t xml:space="preserve"> 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
 </t>
     </r>
     <r>
@@ -3597,7 +3380,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5034
+      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5032
 </t>
     </r>
     <r>
@@ -3637,7 +3420,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92201/artclView.do?layout=unknown</t>
+      <t xml:space="preserve"> 수강관련 학사공지: https://www.hknu.ac.kr/bbs/kor/70/91760/artclView.do?layout=unknown</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3649,17 +3432,17 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>📝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 수강 관련 안내
+      <t>👨‍🏫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교직 이수 안내
 </t>
     </r>
     <r>
@@ -3679,7 +3462,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 수강신청:
+      <t xml:space="preserve"> 교직과정이란?
 </t>
     </r>
     <r>
@@ -3699,7 +3482,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 매 학기 개강 전 수강신청 기간에 수강신청 시스템(http://sugang.hknu.ac.kr)에서 신청
+      <t xml:space="preserve"> 일반 전공 수업을 들으면서, 추가로 교육학 및 교직 관련 과목을 이수하여 교사 자격증을 취득하는 제도
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 자격:
 </t>
     </r>
     <r>
@@ -3719,27 +3522,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 수강신청 정정기간에 과목 변경 가능
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 수강철회:
+      <t xml:space="preserve"> 교직과정 설치 전공을 이수하고 있거나 이수할 예정인 학생
 </t>
     </r>
     <r>
@@ -3759,7 +3542,109 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 학기 중 수강철회 기간에 신청 가능
+      <t xml:space="preserve"> 직전학기까지 33학점 이상 취득한 학생
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5036
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90976/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업/졸업유예/조기졸업 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업유예, 조기졸업 접수 시기:
 </t>
     </r>
     <r>
@@ -3779,27 +3664,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 재수강과 다름 (재수강은 이전 성적 대체)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 성적 이의신청:
+      <t xml:space="preserve"> 2월 졸업: 1월에 접수
 </t>
     </r>
     <r>
@@ -3819,7 +3684,151 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 성적 공시 후 정정기간 내 신청
+      <t xml:space="preserve"> 8월 졸업: 7월에 접수
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5036
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업(수료) 안내: https://www.hknu.ac.kr/kor/532/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업유예 참고: https://www.hknu.ac.kr/bbs/kor/70/96753/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 조기졸업 참고: https://www.hknu.ac.kr/bbs/kor/70/96752/artclView.do?layout=unknown
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 소단위전공과정(마이크로디그리)란?
+적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 특징:
 </t>
     </r>
     <r>
@@ -3839,109 +3848,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 성적확인: 학사시스템(https://info.hknu.ac.kr)에서 조회
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5032
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 수강관련 학사공지: https://www.hknu.ac.kr/bbs/kor/70/91760/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>👨‍🏫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교직 이수 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교직과정이란?
+      <t xml:space="preserve"> 과정별 8~12학점 이수
 </t>
     </r>
     <r>
@@ -3961,27 +3868,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 일반 전공 수업을 들으면서, 추가로 교육학 및 교직 관련 과목을 이수하여 교사 자격증을 취득하는 제도
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 신청 자격:
+      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
 </t>
     </r>
     <r>
@@ -4001,7 +3888,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 교직과정 설치 전공을 이수하고 있거나 이수할 예정인 학생
+      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
 </t>
     </r>
     <r>
@@ -4021,109 +3908,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 직전학기까지 33학점 이상 취득한 학생
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5036
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/90976/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>⏰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업/졸업유예/조기졸업 안내
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업유예, 조기졸업 접수 시기:
+      <t xml:space="preserve"> 이수건수 제한 없음
 </t>
     </r>
     <r>
@@ -4143,7 +3928,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 2월 졸업: 1월에 접수
+      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 마이크로디그리 과정 목록 (총 55개):
 </t>
     </r>
     <r>
@@ -4163,151 +3968,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 8월 졸업: 7월에 접수
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5036
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업(수료) 안내: https://www.hknu.ac.kr/kor/532/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업유예 참고: https://www.hknu.ac.kr/bbs/kor/70/96753/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 조기졸업 참고: https://www.hknu.ac.kr/bbs/kor/70/96752/artclView.do?layout=unknown
-</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 소단위전공과정(마이크로디그리)란?
-적은 학점으로 다양한 전공을 경험해 볼 수 있는 제도입니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 특징:
+      <t xml:space="preserve"> AI·반도체·IT (20개): 사물인터넷, 통신공학, AI보안, AI화학공학, 반도체 설계/공정/소재/부품장비, AIoT보안, 미래모빌리티, 첨단소재공학 등
 </t>
     </r>
     <r>
@@ -4327,7 +3988,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 과정별 8~12학점 이수
+      <t xml:space="preserve"> 농생명·바이오·식품 (9개): 식품품질관리, 반려동물, 유전체 육종번식, 축산식품과 HACCP, 생명공학연구실습, 식물원학 등
 </t>
     </r>
     <r>
@@ -4347,7 +4008,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 본인 전공과목과 중복 인정 가능
+      <t xml:space="preserve"> 인문·사회·교육 (8개): 공공 PR, 정책분석평가, 의료수어통역, 청소년상담가과정, 유아 교과 수업설계 등
 </t>
     </r>
     <r>
@@ -4367,7 +4028,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 타 전공 3개 교과목 이상 이수 시 연계전공 신청 가능
+      <t xml:space="preserve"> 디자인·문화·예술 (7개): 브랜드 콘텐츠, 내러티브 디자인, 컴퓨터음악, 3D 프린팅 디자이너, 귀금속보석공예 등
 </t>
     </r>
     <r>
@@ -4387,7 +4048,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 이수건수 제한 없음
+      <t xml:space="preserve"> 에너지·환경·안전 (6개): 인프라 재난방재, 바이오에너지, 산업보건 및 위생, 탄소중립 전기에너지 등
 </t>
     </r>
     <r>
@@ -4407,27 +4068,419 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 이수 시 별도의 이수증 발급
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 마이크로디그리 과정 목록 (총 55개):
+      <t xml:space="preserve"> 경영·재무·마케팅 (5개): 그로스마케터 과정, 재무빅데이터분석 전문가, 글로벌 비즈니스 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 성적/수강 확인 안내
+성적확인, 이수학점 확인, 수강조회 등
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사시스템에서 확인: https://info.hknu.ac.kr
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 이 챗봇은 유연학사제도(다전공) 전용입니다. 학사일정 관련 자세한 문의는 교육학사혁신팀(031-670-5036)으로 연락해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 수강신청, 변경, 철회 관련 안내: https://www.hknu.ac.kr/kor/524/subview.do
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 시험/성적/학사경고 안내 참조: https://www.hknu.ac.kr/kor/527/subview.do</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학생설계전공은 학생 본인이 주도적으로 교육과정을 설계하는 제도입니다. 본교에 개설된 교과목 중에서 학생이 직접 선택·조합하여 54학점 이내로 교육과정을 편성해야 합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 이수 요건:
 </t>
     </r>
     <r>
@@ -4447,7 +4500,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> AI·반도체·IT (20개): 사물인터넷, 통신공학, AI보안, AI화학공학, 반도체 설계/공정/소재/부품장비, AIoT보안, 미래모빌리티, 첨단소재공학 등
+      <t xml:space="preserve"> 원 전공: 전필 포함 39학점 이상 (인문·사회계열(법학전공 제외) 36학점)
 </t>
     </r>
     <r>
@@ -4467,7 +4520,562 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 농생명·바이오·식품 (9개): 식품품질관리, 반려동물, 유전체 육종번식, 축산식품과 HACCP, 생명공학연구실습, 식물원학 등
+      <t xml:space="preserve"> 학생설계전공: 설계한 전공 교과목 39학점 이상
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 원 전공과 학생설계전공 교과목이 중복될 경우, 해당 학부(전공)에서 지정하는 별도 교과목을 추가로 이수해야 합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 커리큘럼 설계 시 반드시 지도교수와 사전 상담을 진행하시고, 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 원 전공에서 이미 이수한 교과목이 복수전공의 교과목과 동일한 경우에는, 해당 복수전공 학부(전공)에서 지정하는 다른 교과목을 추가로 이수해야 합니다.
+즉, 중복 이수로 양쪽을 동시에 인정받는 것은 불가합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 중복 여부 및 대체 가능 과목은 복수전공 해당 학부(전공) 사무실 또는 교육학사혁신팀(031-670-5035)에 문의해 주시기 바랍니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 원칙적으로 복수전공에서 이수한 교과목은 복수전공 학점으로만 인정되며, 이를 원 전공의 전공선택 학점으로 동시에 인정받는 것은 불가합니다.
+다만, 교육과정 구성에 따라 예외적인 경우가 있을 수 있으므로, 정확한 사항은 본인 소속 학부(전공) 사무실 또는 교육학사혁신팀(031-670-5035)에 개별 확인하시기 바랍니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학생설계전공 이수 신청 시 지도교수와의 사전 상담이 필요합니다.
+학생이 직접 교육과정을 설계하는 제도인 만큼, 교과목 선정의 적절성과 학업 방향에 대해 지도교수의 검토와 확인을 받아야 합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학생설계전공 교육과정은 기본적으로 본교에 개설된 교과목을 조합하여 편성하는 것을 원칙으로 합니다.
+타 대학교 수업의 경우, 학점교류 제도를 통해 취득한 학점이 학생설계전공에 인정될 수 있는지 여부는 상황에 따라 다를 수 있습니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 커리큘럼 편성 전에 반드시 지도교수님 및 교육학사혁신팀 담당자(031-670-5034)와 사전 상담을 받으시기 바랍니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 계열이 다른 전공으로 복수전공을 신청하면 초반에는 학습 부담이 클 수 있습니다. 특히 수학, 과학 기초 지식 차이로 어려움을 겪는 경우가 많습니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 무리하게 바로 복수전공에 도전하기보다는, 먼저 소단위전공과정(마이크로디그리)이나 연계전공 등 비교적 부담이 적은 유연학사제도로 해당 분야를 경험해보신 후, 적성과 흥미를 확인하고 복수전공을 결정하시길 권장합니다.
+궁금한 점은 교육학사혁신팀(031-670-5035) 또는 해당 전공 사무실로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전공 간 시너지는 개인의 진로 목표와 관심 분야에 따라 크게 달라지므로, 일률적으로 추천드리기 어렵습니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 사이드 메뉴의 '다전공 제도 안내'에서 각 전공별 교육과정을 먼저 살펴보시고, 상담이 필요하시면 해당 전공 사무실 또는 교육학사혁신팀(031-670-5035)으로 연락 주시면 도움드리겠습니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공은 졸업종합시험(논문 포함) 대상에 해당하지 않습니다.
+원 전공의 졸업종합시험 합격 요건만 충족하시면 됩니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 연계전공 신청 방법과 시기는 복수전공과 유사하며, 매 학기 학사공지를 통해 안내됩니다.
+연계전공은 관련 전공의 교과목을 9학점 이상 이수하는 방식으로 운영됩니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 편입학생도 재학 중 복수전공 신청이 가능합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 신청 시기와 방법 등은 학사공지를 참고해 주세요: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 자체는 휴학 중에도 가능할 수 있으나, 실제 이수(수업 수강)는 해당 학기에 반드시 복학한 상태여야 합니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 정확한 신청 가능 여부는 교육학사혁신팀(031-670-5035)에 확인하시기 바랍니다.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청은 학기별로 정해진 기간에만 가능합니다.
+신청 기간은 매 학기초, 학기말(2회) 학사공지를 통해 안내되므로, 홈페이지 공지사항을 확인하시기 바랍니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전과(원 전공 변경)와 복수전공은 별개의 제도입니다.
+전과 신청 시 기존 복수전공 이수 현황이 어떻게 처리되는지는 경우에 따라 달라질 수 있습니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업식 일정
 </t>
     </r>
     <r>
@@ -4487,7 +5095,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 인문·사회·교육 (8개): 공공 PR, 정책분석평가, 의료수어통역, 청소년상담가과정, 유아 교과 수업설계 등
+      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
 </t>
     </r>
     <r>
@@ -4507,7 +5115,1650 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 디자인·문화·예술 (7개): 브랜드 콘텐츠, 내러티브 디자인, 컴퓨터음악, 3D 프린팅 디자이너, 귀금속보석공예 등
+      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 교육학사혁신 031-670-5035
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>학사지원팀,교육학사혁신팀, 학사지원팀연락처,교육학사혁신팀연락처,학사지원팀전화번호,교육학사혁신팀전화번호, 학사제도문의,학사업무문의,학사업무연락처,학사지원팀문의처,학사제도연락처,학사제도전화번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 업무별 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회(문의: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리(문의: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전과 및 재입학, 학점인정(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">OCU </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">등), 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명(문의: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">☎ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교육학사혁신팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5033)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 계절수업, 특별학기 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류(문의: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5034)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 졸업종합시험, 졸업인증, 조기졸업, 졸업유예, 졸업사정, 교직과정, 교원자격증(문의: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5036)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>강의평가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, SWAN,  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자유학기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학위수여</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학위수여식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>문의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>교육학사혁신팀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 031-670-5035)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">  평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5034
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 계절수업 안내 참조: https://www.hknu.ac.kr/kor/526/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류 안내 참조: https://www.hknu.ac.kr/kor/528/subview.do
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전과 및 재입학, 전공배정, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>군복무중</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>취득학점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(OCU), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5037
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전과 안내 참조: https://www.hknu.ac.kr/kor/536/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 재입학 안내 참조: https://www.hknu.ac.kr/kor/538/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 전공배정 안내 참조: https://www.hknu.ac.kr/kor/531/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 휴·복학 안내 참조: https://www.hknu.ac.kr/kor/537/subview.do
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 증명서 안내 참조: https://www.hknu.ac.kr/kor/548/subview.do
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▶</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정, 교원자격증, 강의평가, SWAN, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생 관련 문의
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교육학사혁신팀 031-670-5035, 5036
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 교직과정 모집 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/92919/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 자유학기 모집 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/96305/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학위수여식 관련 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 강의평가 관련 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/96124/artclView.do?layout=unknown
+</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 2027-1학기 유연학사제도(다전공) 모집 신청기간: 2026. 10. 6.(화) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>~ 10. 16.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>96137</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2027-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유연학사제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신청기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 2026. 10. 6.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>) ~ 10. 16.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>96137</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2027-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>학기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유연학사제도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>다전공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모집</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신청기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: 2026. 10. 6.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>) ~ 10. 16.(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>96137</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>/artclView.do?layout=unknow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 안내
 </t>
     </r>
     <r>
@@ -4527,7 +6778,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 에너지·환경·안전 (6개): 인프라 재난방재, 바이오에너지, 산업보건 및 위생, 탄소중립 전기에너지 등
+      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
 </t>
     </r>
     <r>
@@ -4547,27 +6798,106 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 경영·재무·마케팅 (5개): 그로스마케터 과정, 재무빅데이터분석 전문가, 글로벌 비즈니스 등
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 과정별 상세 내용은 '마이크로디그리 목록 알려줘'라고 질문해주세요!</t>
+      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>국립대학육성사업으로 다전공 참여 장학금, 이수완료 장학금 제도 운영(초과학기자도 수혜 가능, 학위수여유예자는 제외)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 재무팀 031-670-5476
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4579,387 +6909,37 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 성적/수강 확인 안내
-성적확인, 이수학점 확인, 수강조회 등
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학사시스템에서 확인: https://info.hknu.ac.kr
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5032
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학사일정(개강일, 종강일, 시험기간, 방학 등)은 학교 홈페이지에서 확인하세요.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학사일정 바로가기: https://www.hknu.ac.kr/kor/646/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 이 챗봇은 유연학사제도(다전공) 전용입니다. 학사일정 관련 자세한 문의는 교육학사혁신팀(031-670-5036)으로 연락해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회 관련 문의
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 수강신청, 변경, 철회 관련 안내: https://www.hknu.ac.kr/kor/524/subview.do
-</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리 관련 문의
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 시험/성적/학사경고 안내 참조: https://www.hknu.ac.kr/kor/527/subview.do</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학생설계전공은 학생 본인이 주도적으로 교육과정을 설계하는 제도입니다. 본교에 개설된 교과목 중에서 학생이 직접 선택·조합하여 54학점 이내로 교육과정을 편성해야 합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 이수 요건:
+      <t>🔄</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류 안내
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학점교류란?
 </t>
     </r>
     <r>
@@ -4979,7 +6959,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 원 전공: 전필 포함 39학점 이상 (인문·사회계열(법학전공 제외) 36학점)
+      <t xml:space="preserve"> 국내외 대학에서 이수한 학점을 본교 학점으로 인정받는 제도
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 종류:
 </t>
     </r>
     <r>
@@ -4999,604 +6999,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 학생설계전공: 설계한 전공 교과목 39학점 이상
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 원 전공과 학생설계전공 교과목이 중복될 경우, 해당 학부(전공)에서 지정하는 별도 교과목을 추가로 이수해야 합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 커리큘럼 설계 시 반드시 지도교수와 사전 상담을 진행하시고, 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>⚠️</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 원 전공에서 이미 이수한 교과목이 복수전공의 교과목과 동일한 경우에는, 해당 복수전공 학부(전공)에서 지정하는 다른 교과목을 추가로 이수해야 합니다.
-즉, 중복 이수로 양쪽을 동시에 인정받는 것은 불가합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 중복 여부 및 대체 가능 과목은 복수전공 해당 학부(전공) 사무실 또는 교육학사혁신팀(031-670-5035)에 문의해 주시기 바랍니다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 원칙적으로 복수전공에서 이수한 교과목은 복수전공 학점으로만 인정되며, 이를 원 전공의 전공선택 학점으로 동시에 인정받는 것은 불가합니다.
-다만, 교육과정 구성에 따라 예외적인 경우가 있을 수 있으므로, 정확한 사항은 본인 소속 학부(전공) 사무실 또는 교육학사혁신팀(031-670-5035)에 개별 확인하시기 바랍니다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학생설계전공 이수 신청 시 지도교수와의 사전 상담이 필요합니다.
-학생이 직접 교육과정을 설계하는 제도인 만큼, 교과목 선정의 적절성과 학업 방향에 대해 지도교수의 검토와 확인을 받아야 합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학생설계전공 교육과정은 기본적으로 본교에 개설된 교과목을 조합하여 편성하는 것을 원칙으로 합니다.
-타 대학교 수업의 경우, 학점교류 제도를 통해 취득한 학점이 학생설계전공에 인정될 수 있는지 여부는 상황에 따라 다를 수 있습니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 커리큘럼 편성 전에 반드시 지도교수님 및 교육학사혁신팀 담당자(031-670-5034)와 사전 상담을 받으시기 바랍니다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 계열이 다른 전공으로 복수전공을 신청하면 초반에는 학습 부담이 클 수 있습니다. 특히 수학, 과학 기초 지식 차이로 어려움을 겪는 경우가 많습니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 무리하게 바로 복수전공에 도전하기보다는, 먼저 소단위전공과정(마이크로디그리)이나 연계전공 등 비교적 부담이 적은 유연학사제도로 해당 분야를 경험해보신 후, 적성과 흥미를 확인하고 복수전공을 결정하시길 권장합니다.
-궁금한 점은 교육학사혁신팀(031-670-5035) 또는 해당 전공 사무실로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전공 간 시너지는 개인의 진로 목표와 관심 분야에 따라 크게 달라지므로, 일률적으로 추천드리기 어렵습니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 사이드 메뉴의 '다전공 제도 안내'에서 각 전공별 교육과정을 먼저 살펴보시고, 상담이 필요하시면 해당 전공 사무실 또는 교육학사혁신팀(031-670-5035)으로 연락 주시면 도움드리겠습니다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 융합전공과 융합부전공 모두 이수 완료 시 졸업증명서에 표기됩니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 부전공은 졸업종합시험(논문 포함) 대상에 해당하지 않습니다.
-원 전공의 졸업종합시험 합격 요건만 충족하시면 됩니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 연계전공 신청 방법과 시기는 복수전공과 유사하며, 매 학기 학사공지를 통해 안내됩니다.
-연계전공은 관련 전공의 교과목을 9학점 이상 이수하는 방식으로 운영됩니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 자세한 사항은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 편입학생도 재학 중 복수전공 신청이 가능합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 신청 시기와 방법 등은 학사공지를 참고해 주세요: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 신청 자체는 휴학 중에도 가능할 수 있으나, 실제 이수(수업 수강)는 해당 학기에 반드시 복학한 상태여야 합니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 정확한 신청 가능 여부는 교육학사혁신팀(031-670-5035)에 확인하시기 바랍니다.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 신청은 학기별로 정해진 기간에만 가능합니다.
-신청 기간은 매 학기초, 학기말(2회) 학사공지를 통해 안내되므로, 홈페이지 공지사항을 확인하시기 바랍니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학사공지: https://www.hknu.ac.kr/bbs/kor/70/96137/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전과(원 전공 변경)와 복수전공은 별개의 제도입니다.
-전과 신청 시 기존 복수전공 이수 현황이 어떻게 처리되는지는 경우에 따라 달라질 수 있습니다.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🎓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업식 일정
+      <t xml:space="preserve"> 국내외 대학 학점교류 (협약 대학 간)
 </t>
     </r>
     <r>
@@ -5616,7 +7019,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 전기 졸업식: 매년 2월 중순
+      <t xml:space="preserve"> 계절학기 (여름/겨울 방학 중 타교 수강)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 유의사항:
 </t>
     </r>
     <r>
@@ -5636,1056 +7059,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 후기 졸업식: 매년 8월 중순
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 교육학사혁신 031-670-5035
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 정확한 일정은 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>학사지원팀,교육학사혁신팀, 학사지원팀연락처,교육학사혁신팀연락처,학사지원팀전화번호,교육학사혁신팀전화번호, 학사제도문의,학사업무문의,학사업무연락처,학사지원팀문의처,학사제도연락처,학사제도전화번호</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 업무별 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 강의개설 및 시간표 편성, 강의계획서, 수강신청, 수강신청변경, 교과목 설·폐강, 수강철회(문의: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 성적입력 및 열람, 성적 정정, 성적 확정, 학사경고 및 제적처리(문의: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5032)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전과 및 재입학, 학점인정(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">OCU </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">등), 전공배정, 출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명(문의: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">☎ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교육학사혁신팀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 031-670-5033)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 계절수업, 특별학기 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류(문의: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5034)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 졸업종합시험, 졸업인증, 조기졸업, 졸업유예, 졸업사정, 교직과정, 교원자격증(문의: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5036)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>강의평가</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, SWAN,  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자유학기</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>학위수여</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>학위수여식</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>문의</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>교육학사혁신팀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 031-670-5035)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">  평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 계절수업, 이수구분 변경, 대체·유사과목 성적 삭제, 학점교류 관련 문의
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5034
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 계절수업 안내 참조: https://www.hknu.ac.kr/kor/526/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학점교류 안내 참조: https://www.hknu.ac.kr/kor/528/subview.do
-</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전과 및 재입학, 전공배정, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>군복무중</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>취득학점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>인정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(OCU), </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">출석인정, 학적변동(휴·복학, 제적 등), 성적·졸업증명서 등 각종 제증명 관련 문의
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5037
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전과 안내 참조: https://www.hknu.ac.kr/kor/536/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 재입학 안내 참조: https://www.hknu.ac.kr/kor/538/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 전공배정 안내 참조: https://www.hknu.ac.kr/kor/531/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 휴·복학 안내 참조: https://www.hknu.ac.kr/kor/537/subview.do
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 증명서 안내 참조: https://www.hknu.ac.kr/kor/548/subview.do
-</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 해당 업무의 담당 연락처를 안내해 드릴게요!
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>▶</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교직과정, 교원자격증, 강의평가, SWAN, 자유학기, 학위수여, 학위수여식, 온라인 학위과정, 복수학위 및 공동학위, 시간제 등록생 관련 문의
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교육학사혁신팀 031-670-5035, 5036
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 교직과정 모집 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/92919/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 자유학기 모집 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/96305/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 학위수여식 관련 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/92840/artclView.do?layout=unknown
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 강의평가 관련 안내 참조: https://www.hknu.ac.kr/bbs/kor/70/96124/artclView.do?layout=unknown
-</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>💰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 등록금 안내
+      <t xml:space="preserve"> 사전에 학점인정 신청 필요
 </t>
     </r>
     <r>
@@ -6705,7 +7079,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 원전공 기준의 등록금을 납부하면 됨
+      <t xml:space="preserve"> 이수구분(전필, 전선, 교양 등) 확인 후 신청
 </t>
     </r>
     <r>
@@ -6725,7 +7099,27 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 다전공을 신청해도 추가 등록금 없음!
+      <t xml:space="preserve"> 전공 및 교육학사혁신팀 승인 필요
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 문의: 교육학사혁신팀 031-670-5034
 </t>
     </r>
     <r>
@@ -6735,96 +7129,61 @@
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
       </rPr>
-      <t>▸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t>☆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 학사공지 참조: https://www.hknu.ac.kr/bbs/kor/70/92201/artclView.do?layout=unknown</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>다전공 참여 장학금, 이수완료 장학금 제도 운영(초과학기자도 수혜 가능(국립대학육성사업))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 문의: 재무팀 031-670-5476
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>☆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 평일 근무시간(09:00~18:00)에 연락해 주세요. * 점심시간(12:00~13:00) 제외
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>🔗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 등록금 고지, 환불 등은 학교 홈페이지 참조: https://www.hknu.ac.kr/bbs/kor/69/94055/artclView.do?layout=unknown</t>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 부전공을 이수 완료한 경우 학위기 및 성적증명서에 부전공 이수 사실이 표기됩니다.
+이수 중인 상태에서는 표기되지 않으며, 졸업 시점에 최종 확정됩니다.</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -6836,26 +7195,6 @@
         <rFont val="Segoe UI Emoji"/>
         <family val="2"/>
       </rPr>
-      <t>📅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 다전공 신청 기간: 매 학기 초(4월, 10월)와 학기 말(6월, 12월), 학기별 2회 모집.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
       <t>📌</t>
     </r>
     <r>
@@ -6866,44 +7205,50 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 2026-2학기 유연학사제도(다전공) 모집 신청기간: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8</t>
+      <t xml:space="preserve"> 융합전공과 융합부전공 모두 이수 완료 시 학위기 및 성적증명서에 표기됩니다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 궁금한 사항은 교육학사혁신팀(031-670-5035)으로 문의해 주세요.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📌</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">월까지
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 복수전공을 이수하면 원 전공과 복수전공 2개의 학위가 정식으로 발급되며, 두 학위 모두 학위기 및 성적증명서에 기재됩니다.
 </t>
     </r>
     <r>
@@ -6919,39 +7264,12 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> 신청서 양식 및 정확한 일정은 학사공지 확인: https://www.hknu.ac.kr/bbs/kor/70/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>96137</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/artclView.do?layout=unknow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 대학원 지원 시 복수전공 학위가 입학 요건이나 전형에 어떻게 반영되는지는 대학원마다 다를 수 있으므로, 지원하고자 하는 대학원 사무실에 직접 확인하시길 권장합니다.</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -7024,14 +7342,16 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Cambria Math"/>
-      <family val="2"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Segoe UI Symbol"/>
-      <family val="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -7069,7 +7389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -7077,6 +7397,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -7416,7 +7742,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F120"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
@@ -7455,10 +7781,10 @@
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="85.5">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -7475,10 +7801,10 @@
         <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="85.5">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -7495,10 +7821,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="85.5">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -7515,30 +7841,30 @@
         <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="62" customHeight="1">
-      <c r="A6" t="s">
-        <v>358</v>
-      </c>
-      <c r="B6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="5" customFormat="1">
+      <c r="A6" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="85.5">
+      <c r="F6" s="6" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -7555,10 +7881,10 @@
         <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="85.5">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -7575,10 +7901,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="85.5">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -7595,7 +7921,7 @@
         <v>10</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7612,7 +7938,7 @@
         <v>33</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7629,7 +7955,7 @@
         <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7646,7 +7972,7 @@
         <v>37</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -7663,7 +7989,7 @@
         <v>39</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -7680,7 +8006,7 @@
         <v>41</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -7697,7 +8023,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -7717,7 +8043,7 @@
         <v>46</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7737,7 +8063,7 @@
         <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7754,7 +8080,7 @@
         <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -7771,7 +8097,7 @@
         <v>53</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -7788,7 +8114,7 @@
         <v>55</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7805,7 +8131,7 @@
         <v>57</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7822,7 +8148,7 @@
         <v>59</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7839,7 +8165,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7859,7 +8185,7 @@
         <v>46</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7879,7 +8205,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7896,7 +8222,7 @@
         <v>68</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7913,7 +8239,7 @@
         <v>70</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7930,7 +8256,7 @@
         <v>72</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7947,7 +8273,7 @@
         <v>74</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7964,7 +8290,7 @@
         <v>76</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7981,7 +8307,7 @@
         <v>78</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -8001,7 +8327,7 @@
         <v>46</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -8021,7 +8347,7 @@
         <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8467,7 +8793,7 @@
         <v>162</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -8487,7 +8813,7 @@
         <v>166</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -8504,7 +8830,7 @@
         <v>169</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -8521,7 +8847,7 @@
         <v>172</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -8541,7 +8867,7 @@
         <v>176</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -8558,7 +8884,7 @@
         <v>179</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -8575,7 +8901,7 @@
         <v>182</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -8595,7 +8921,7 @@
         <v>46</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -8632,7 +8958,7 @@
         <v>190</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -8652,7 +8978,7 @@
         <v>194</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -8672,7 +8998,7 @@
         <v>194</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -8692,7 +9018,7 @@
         <v>194</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -8712,7 +9038,7 @@
         <v>194</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -8732,7 +9058,7 @@
         <v>194</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -8752,7 +9078,7 @@
         <v>194</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -8772,7 +9098,7 @@
         <v>194</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -8792,7 +9118,7 @@
         <v>194</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -8928,7 +9254,7 @@
         <v>233</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -8945,7 +9271,7 @@
         <v>236</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -8962,7 +9288,7 @@
         <v>238</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -8979,7 +9305,7 @@
         <v>240</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -8996,7 +9322,7 @@
         <v>242</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -9013,7 +9339,7 @@
         <v>244</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -9027,10 +9353,10 @@
         <v>161</v>
       </c>
       <c r="D89" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -9050,7 +9376,7 @@
         <v>249</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -9070,7 +9396,7 @@
         <v>252</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -9090,7 +9416,7 @@
         <v>255</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -9130,7 +9456,7 @@
         <v>261</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -9150,7 +9476,7 @@
         <v>264</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -9167,7 +9493,7 @@
         <v>266</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -9207,7 +9533,7 @@
         <v>273</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -9264,12 +9590,12 @@
         <v>283</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>284</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B102" t="s">
         <v>109</v>
@@ -9278,18 +9604,18 @@
         <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E102" t="s">
         <v>252</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B103" t="s">
         <v>109</v>
@@ -9298,18 +9624,18 @@
         <v>15</v>
       </c>
       <c r="D103" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E103" t="s">
         <v>252</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B104" t="s">
         <v>109</v>
@@ -9318,18 +9644,18 @@
         <v>12</v>
       </c>
       <c r="D104" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E104" t="s">
         <v>252</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B105" t="s">
         <v>210</v>
@@ -9338,15 +9664,15 @@
         <v>8</v>
       </c>
       <c r="D105" t="s">
+        <v>292</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B106" t="s">
         <v>192</v>
@@ -9355,18 +9681,18 @@
         <v>23</v>
       </c>
       <c r="D106" t="s">
+        <v>295</v>
+      </c>
+      <c r="E106" t="s">
         <v>296</v>
       </c>
-      <c r="E106" t="s">
-        <v>297</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B107" t="s">
         <v>109</v>
@@ -9375,18 +9701,18 @@
         <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E107" t="s">
         <v>252</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B108" t="s">
         <v>135</v>
@@ -9395,18 +9721,18 @@
         <v>12</v>
       </c>
       <c r="D108" t="s">
+        <v>301</v>
+      </c>
+      <c r="E108" t="s">
         <v>302</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B109" t="s">
         <v>135</v>
@@ -9415,18 +9741,18 @@
         <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E109" t="s">
         <v>252</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B110" t="s">
         <v>32</v>
@@ -9435,32 +9761,32 @@
         <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
+        <v>309</v>
+      </c>
+      <c r="B111" t="s">
         <v>310</v>
-      </c>
-      <c r="B111" t="s">
-        <v>311</v>
       </c>
       <c r="C111" t="s">
         <v>12</v>
       </c>
       <c r="D111" t="s">
+        <v>311</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>312</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B112" t="s">
         <v>109</v>
@@ -9469,15 +9795,15 @@
         <v>12</v>
       </c>
       <c r="D112" t="s">
+        <v>314</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B113" t="s">
         <v>32</v>
@@ -9486,15 +9812,15 @@
         <v>12</v>
       </c>
       <c r="D113" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B114" t="s">
         <v>109</v>
@@ -9503,18 +9829,18 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E114" t="s">
         <v>252</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>321</v>
+        <v>388</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B115" t="s">
         <v>50</v>
@@ -9523,15 +9849,15 @@
         <v>8</v>
       </c>
       <c r="D115" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B116" t="s">
         <v>109</v>
@@ -9540,18 +9866,18 @@
         <v>12</v>
       </c>
       <c r="D116" t="s">
+        <v>324</v>
+      </c>
+      <c r="E116" t="s">
+        <v>325</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="E116" t="s">
-        <v>327</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B117" t="s">
         <v>109</v>
@@ -9560,18 +9886,18 @@
         <v>12</v>
       </c>
       <c r="D117" t="s">
+        <v>328</v>
+      </c>
+      <c r="E117" t="s">
+        <v>329</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>330</v>
-      </c>
-      <c r="E117" t="s">
-        <v>331</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
@@ -9580,15 +9906,15 @@
         <v>8</v>
       </c>
       <c r="D118" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B119" t="s">
         <v>67</v>
@@ -9597,10 +9923,10 @@
         <v>12</v>
       </c>
       <c r="D119" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:6">
